--- a/output/pdf_financials_xlsx/EMM.xlsx
+++ b/output/pdf_financials_xlsx/EMM.xlsx
@@ -1344,49 +1344,49 @@
         <v>1.816747</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6.006225</v>
+        <v>-6.006225</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>11.227622</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>7.943952</v>
+        <v>0.034104</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>6.956965</v>
+        <v>0.126065</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>23.40834</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-0.351048</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.324009</v>
+        <v>-1.324009</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.05302</v>
+        <v>-2.05302</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.985181</v>
+        <v>-1.614773</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.119789</v>
+        <v>-2.119789</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>5.112223</v>
+        <v>-5.112223</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>5.42364</v>
+        <v>-5.42364</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>4.81663</v>
+        <v>-4.81663</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>9.147650000000001</v>
+        <v>-9.147650000000001</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>8.740857999999999</v>
+        <v>-8.740857999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1661,52 +1661,52 @@
         <v>-0.000664</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.816747</v>
+        <v>-1.816747</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>6.006225</v>
+        <v>-6.006225</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5.613811</v>
+        <v>-5.613811</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.954924</v>
+        <v>-3.954924</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.41545</v>
+        <v>-3.41545</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11.70417</v>
+        <v>-11.70417</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-0.351048</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.324009</v>
+        <v>-1.324009</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.05302</v>
+        <v>-2.05302</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.799977</v>
+        <v>-1.799977</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.119789</v>
+        <v>-2.119789</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>5.112223</v>
+        <v>-5.112223</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>5.42364</v>
+        <v>-5.42364</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>4.81663</v>
+        <v>-4.81663</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>9.147650000000001</v>
+        <v>-9.147650000000001</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>8.740857999999999</v>
+        <v>-8.740857999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1850,52 +1850,52 @@
         <v>-0.000664</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.816747</v>
+        <v>-1.816747</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6.006225</v>
+        <v>-6.006225</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.613811</v>
+        <v>-5.613811</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.954924</v>
+        <v>-3.954924</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.41545</v>
+        <v>-3.41545</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>11.70417</v>
+        <v>-11.70417</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-0.351048</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.324009</v>
+        <v>-1.324009</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.05302</v>
+        <v>-2.05302</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.799977</v>
+        <v>-1.799977</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.119789</v>
+        <v>-2.119789</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>5.112223</v>
+        <v>-5.112223</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>5.42364</v>
+        <v>-5.42364</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4.81663</v>
+        <v>-4.81663</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>9.147650000000001</v>
+        <v>-9.147650000000001</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>8.740857999999999</v>
+        <v>-8.740857999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2043,22 +2043,22 @@
         <v>-0.022133</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>20.186078</v>
+        <v>-20.186078</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>35.330735</v>
+        <v>-35.330735</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>43.183162</v>
+        <v>-43.183162</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>56.498914</v>
+        <v>-56.498914</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>56.924167</v>
+        <v>-56.924167</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>61.600895</v>
+        <v>-61.600895</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -2066,31 +2066,31 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>66.20045</v>
+        <v>-66.20045</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>68.434</v>
+        <v>-68.434</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>89.99885</v>
+        <v>-89.99885</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>105.98945</v>
+        <v>-105.98945</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>170.407433</v>
+        <v>-170.407433</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>180.788</v>
+        <v>-180.788</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>240.8315</v>
+        <v>-240.8315</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>304.921667</v>
+        <v>-304.921667</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>291.361933</v>
+        <v>-291.361933</v>
       </c>
     </row>
     <row r="27">
@@ -2111,49 +2111,49 @@
         <v>1.816747</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6.006225</v>
+        <v>-6.006225</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>11.227622</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>7.943952</v>
+        <v>0.034104</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.956965</v>
+        <v>0.126065</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>23.40834</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.351048</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.324009</v>
+        <v>-1.324009</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.05302</v>
+        <v>-2.05302</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.985181</v>
+        <v>-1.614773</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.119789</v>
+        <v>-2.119789</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>5.112223</v>
+        <v>-5.112223</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>5.42364</v>
+        <v>-5.42364</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.81663</v>
+        <v>-4.81663</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>9.147650000000001</v>
+        <v>-9.147650000000001</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>8.740857999999999</v>
+        <v>-8.740857999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2237,49 +2237,49 @@
         <v>1.816747</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6.006225</v>
+        <v>-6.006225</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>11.227622</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7.943952</v>
+        <v>0.034104</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6.956965</v>
+        <v>0.126065</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>23.40834</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.351048</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.324009</v>
+        <v>-1.324009</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.05302</v>
+        <v>-2.05302</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.985181</v>
+        <v>-1.614773</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.127446</v>
+        <v>-2.112132</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>5.151528</v>
+        <v>-5.072918</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.42364</v>
+        <v>-5.42364</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>4.81663</v>
+        <v>-4.81663</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>9.147650000000001</v>
+        <v>-9.147650000000001</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>8.740857999999999</v>
+        <v>-8.740857999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2397,49 +2397,53 @@
         <v>99.27513297118421</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>50</v>
+        <v>-0</v>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>50.21465386497803</v>
+        <v>11696.6572836031</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>50.906034456117</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>50</v>
+        <v>2809.276960298259</v>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>9.329325638317112</v>
+        <v>-11.46935203895532</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6774,7 +6778,7 @@
         <v>-0.000664</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>1.816747</v>
+        <v>-1.816747</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-6.006225</v>
@@ -6794,7 +6798,7 @@
         <v>-11.70417</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.351048</v>
+        <v>-0.351048</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-1.324009</v>
@@ -6805,7 +6809,7 @@
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>1.799977</v>
+        <v>-1.799977</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>-2.119789</v>
@@ -8150,13 +8154,13 @@
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>2.902556</v>
+        <v>1.922</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1.046058</v>
+        <v>-1.862955</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.264664</v>
       </c>
       <c r="H118" s="1" t="inlineStr">
         <is>
@@ -8164,13 +8168,13 @@
         </is>
       </c>
       <c r="I118" s="3" t="n">
-        <v>10.423646</v>
+        <v>10.394786</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.205058</v>
+        <v>0.19844</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.73</v>
+        <v>0.371271</v>
       </c>
       <c r="L118" s="1" t="inlineStr">
         <is>
@@ -8183,10 +8187,10 @@
         </is>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-1.049256</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-4.970523</v>
       </c>
       <c r="P118" s="3" t="n">
         <v>0</v>
@@ -35910,7 +35914,11 @@
           <t>Additions to exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -36594,7 +36602,7 @@
         </is>
       </c>
       <c r="M259" s="5" t="n">
-        <v>0.351048</v>
+        <v>-0.351048</v>
       </c>
       <c r="N259" s="5" t="n">
         <v>-1.324009</v>
@@ -38446,7 +38454,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -42168,7 +42180,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -44932,7 +44948,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -49416,22 +49436,22 @@
         </is>
       </c>
       <c r="Q380" s="5" t="n">
-        <v>2.119789</v>
+        <v>-2.119789</v>
       </c>
       <c r="R380" s="5" t="n">
         <v>5.112223</v>
       </c>
       <c r="S380" s="5" t="n">
-        <v>5.42364</v>
+        <v>-5.42364</v>
       </c>
       <c r="T380" s="5" t="n">
-        <v>4.81663</v>
+        <v>-4.81663</v>
       </c>
       <c r="U380" s="5" t="n">
-        <v>9.147650000000001</v>
+        <v>-9.147650000000001</v>
       </c>
       <c r="V380" s="5" t="n">
-        <v>8.740857999999999</v>
+        <v>-8.740857999999999</v>
       </c>
     </row>
     <row r="381">
@@ -49620,16 +49640,16 @@
         <v>5.161161</v>
       </c>
       <c r="S382" s="5" t="n">
-        <v>4.929142</v>
+        <v>-4.929142</v>
       </c>
       <c r="T382" s="5" t="n">
-        <v>7.324649</v>
+        <v>-7.324649</v>
       </c>
       <c r="U382" s="5" t="n">
-        <v>6.055342</v>
+        <v>-6.055342</v>
       </c>
       <c r="V382" s="5" t="n">
-        <v>10.024406</v>
+        <v>-10.024406</v>
       </c>
     </row>
     <row r="383">
@@ -58034,10 +58054,10 @@
         </is>
       </c>
       <c r="Q462" s="5" t="n">
-        <v>2.418363</v>
+        <v>-2.418363</v>
       </c>
       <c r="R462" s="5" t="n">
-        <v>5.161161</v>
+        <v>-5.161161</v>
       </c>
       <c r="S462" t="inlineStr">
         <is>
@@ -61520,10 +61540,10 @@
         </is>
       </c>
       <c r="O495" s="5" t="n">
-        <v>2.05302</v>
+        <v>-2.05302</v>
       </c>
       <c r="P495" s="5" t="n">
-        <v>1.799977</v>
+        <v>-1.799977</v>
       </c>
       <c r="Q495" t="inlineStr">
         <is>
@@ -61725,13 +61745,13 @@
         </is>
       </c>
       <c r="N497" s="5" t="n">
-        <v>1.330157</v>
+        <v>-1.330157</v>
       </c>
       <c r="O497" s="5" t="n">
-        <v>1.998405</v>
+        <v>-1.998405</v>
       </c>
       <c r="P497" s="5" t="n">
-        <v>1.817649</v>
+        <v>-1.817649</v>
       </c>
       <c r="Q497" t="inlineStr">
         <is>
@@ -62257,10 +62277,10 @@
         </is>
       </c>
       <c r="N502" s="5" t="n">
-        <v>1.324009</v>
+        <v>-1.324009</v>
       </c>
       <c r="O502" s="5" t="n">
-        <v>2.05302</v>
+        <v>-2.05302</v>
       </c>
       <c r="P502" t="inlineStr">
         <is>
@@ -66156,10 +66176,10 @@
         </is>
       </c>
       <c r="K539" s="5" t="n">
-        <v>3.41545</v>
+        <v>-3.41545</v>
       </c>
       <c r="L539" s="5" t="n">
-        <v>11.70417</v>
+        <v>-11.70417</v>
       </c>
       <c r="M539" t="inlineStr">
         <is>
@@ -66368,10 +66388,10 @@
         </is>
       </c>
       <c r="K541" s="5" t="n">
-        <v>3.453981</v>
+        <v>-3.453981</v>
       </c>
       <c r="L541" s="5" t="n">
-        <v>11.873206</v>
+        <v>-11.873206</v>
       </c>
       <c r="M541" t="inlineStr">
         <is>
@@ -66476,10 +66496,10 @@
         </is>
       </c>
       <c r="K542" s="5" t="n">
-        <v>3.41545</v>
+        <v>-3.41545</v>
       </c>
       <c r="L542" s="5" t="n">
-        <v>11.70417</v>
+        <v>-11.70417</v>
       </c>
       <c r="M542" t="inlineStr">
         <is>
@@ -68068,10 +68088,10 @@
         </is>
       </c>
       <c r="I557" s="5" t="n">
-        <v>5.613811</v>
+        <v>-5.613811</v>
       </c>
       <c r="J557" s="5" t="n">
-        <v>3.954924</v>
+        <v>-3.954924</v>
       </c>
       <c r="K557" t="inlineStr">
         <is>
@@ -68488,10 +68508,10 @@
         </is>
       </c>
       <c r="I561" s="5" t="n">
-        <v>5.613811</v>
+        <v>-5.613811</v>
       </c>
       <c r="J561" s="5" t="n">
-        <v>3.954924</v>
+        <v>-3.954924</v>
       </c>
       <c r="K561" t="inlineStr">
         <is>
@@ -71553,10 +71573,10 @@
         </is>
       </c>
       <c r="H590" s="5" t="n">
-        <v>6.006225</v>
+        <v>-6.006225</v>
       </c>
       <c r="I590" s="5" t="n">
-        <v>5.613811</v>
+        <v>-5.613811</v>
       </c>
       <c r="J590" t="inlineStr">
         <is>
@@ -71661,10 +71681,10 @@
         </is>
       </c>
       <c r="H591" s="5" t="n">
-        <v>6.006225</v>
+        <v>-6.006225</v>
       </c>
       <c r="I591" s="5" t="n">
-        <v>5.613811</v>
+        <v>-5.613811</v>
       </c>
       <c r="J591" t="inlineStr">
         <is>
@@ -75464,10 +75484,10 @@
         </is>
       </c>
       <c r="G627" s="5" t="n">
-        <v>1.816747</v>
+        <v>-1.816747</v>
       </c>
       <c r="H627" s="5" t="n">
-        <v>6.006225</v>
+        <v>-6.006225</v>
       </c>
       <c r="I627" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EMM.xlsx
+++ b/output/pdf_financials_xlsx/EMM.xlsx
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000664</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00192</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.137987</v>
+        <v>0.138651</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.816747</v>
+        <v>1.818667</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-6.006225</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.137987</v>
+        <v>0.138651</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.816747</v>
+        <v>1.818667</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-6.006225</v>
@@ -2565,7 +2565,7 @@
         <v>0.289572</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3.204345</v>
+        <v>0.289572</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>2.074158</v>
@@ -2577,40 +2577,40 @@
         <v>1.429699</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.033965</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.09401</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.097682</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.021107</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.008758</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>6.338927</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>20.250602</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>11.676017</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>3.051144</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>13.183551</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>3.272871</v>
       </c>
     </row>
     <row r="35">
@@ -2691,7 +2691,7 @@
         <v>0.289572</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>3.204345</v>
+        <v>0.289572</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>2.074158</v>
@@ -2703,40 +2703,40 @@
         <v>1.429699</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.033965</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-0.490909</v>
+        <v>-0.396899</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.097682</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.021107</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.008758</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>6.338927</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>20.250602</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>11.676017</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>3.051144</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>13.183551</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>3.272871</v>
       </c>
     </row>
     <row r="37">
@@ -3459,31 +3459,31 @@
         <v>0.440827</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.090027</v>
+        <v>0.056062</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.06489200000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.667622</v>
+        <v>0.573612</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.353161</v>
+        <v>0.255479</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.172585</v>
+        <v>0.151478</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.070367</v>
+        <v>0.061609</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>6.717955</v>
+        <v>0.379028</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>20.504863</v>
+        <v>0.254261</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>11.878163</v>
+        <v>0.202146</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -22366,7 +22366,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -78560,7 +78560,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">

--- a/output/pdf_financials_xlsx/EMM.xlsx
+++ b/output/pdf_financials_xlsx/EMM.xlsx
@@ -2207,16 +2207,16 @@
         <v>0.039305</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.087468</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.07750700000000001</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.08797099999999999</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>2.713659</v>
       </c>
     </row>
     <row r="29">
@@ -2270,16 +2270,16 @@
         <v>-5.072918</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.42364</v>
+        <v>-5.336172</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.81663</v>
+        <v>-4.739123</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-9.147650000000001</v>
+        <v>-9.059678999999999</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-8.740857999999999</v>
+        <v>-6.027199</v>
       </c>
     </row>
     <row r="30">
@@ -2784,10 +2784,10 @@
         <v>0.041778</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>0.151352</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0</v>
+        <v>0.184819</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>0.041778</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.151352</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>0.184819</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0</v>
@@ -3477,10 +3477,10 @@
         <v>0.061609</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.379028</v>
+        <v>0.227676</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.254261</v>
+        <v>0.069442</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.202146</v>
@@ -6153,22 +6153,22 @@
         <v>23.263072</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0</v>
+        <v>30.48973</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0</v>
+        <v>48.077609</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>0</v>
+        <v>54.285787</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>0</v>
+        <v>54.437438</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>0</v>
+        <v>57.769065</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>0</v>
+        <v>60.352066</v>
       </c>
     </row>
     <row r="89">
@@ -6409,22 +6409,22 @@
         <v>6.704144</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.173754</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>8.298318</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.925431</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>9.25704</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>9.714579000000001</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>9.760201</v>
       </c>
     </row>
     <row r="93">
@@ -7390,7 +7390,7 @@
         <v>1.539755</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.718944</v>
       </c>
       <c r="Q107" s="3" t="n">
         <v>0</v>
@@ -7682,16 +7682,16 @@
         <v>-0.084564</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-4.169707</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-3.731983</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-9.789488</v>
       </c>
       <c r="S111" s="3" t="n">
-        <v>0</v>
+        <v>-6.867371</v>
       </c>
     </row>
     <row r="112">
@@ -8193,16 +8193,16 @@
         <v>-4.970523</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-4.579808</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-1.09367</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-4.44484</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-4.788619</v>
       </c>
     </row>
     <row r="119">
@@ -9409,16 +9409,16 @@
         <v>-0.084564</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-4.169707</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-3.731983</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-9.789488</v>
       </c>
       <c r="S134" s="3" t="n">
-        <v>0</v>
+        <v>-6.867371</v>
       </c>
     </row>
     <row r="135">
@@ -9482,16 +9482,16 @@
         <v>-3.690918</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-4.472385</v>
+        <v>-8.642092</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-3.847124</v>
+        <v>-7.579107</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-5.869965</v>
+        <v>-15.659453</v>
       </c>
       <c r="S135" s="3" t="n">
-        <v>-5.58932</v>
+        <v>-12.456691</v>
       </c>
     </row>
   </sheetData>
@@ -9840,7 +9840,11 @@
           <t>Prepaid and other assets Note 5</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OtherAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -11252,7 +11256,11 @@
           <t>Share capital Note 14 $</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11350,7 +11358,11 @@
           <t>Contributed surplus Note 15</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11916,7 +11928,11 @@
           <t>Share capital Note 12 $</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12012,7 +12028,11 @@
           <t>Contributed surplus Note 13</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -13158,7 +13178,11 @@
           <t>Share capital Note 11 $</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -13258,7 +13282,11 @@
           <t>Contributed surplus Note 12</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -13566,7 +13594,11 @@
           <t>Amount receivable Note 5</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -30088,7 +30120,11 @@
           <t>Depreciation Note 6</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -31120,7 +31156,11 @@
           <t>Additions to property, plant and equipment Note 6</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -31222,7 +31262,11 @@
           <t>Additions to exploration and evaluation expenditures Note 7</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -33814,7 +33858,11 @@
           <t>Depreciation Note 5</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -33918,7 +33966,11 @@
           <t>Stock-based compensation Notes 9,12</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -34542,7 +34594,11 @@
           <t>Additions to property, plant and equipment Note 5</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -34646,7 +34702,11 @@
           <t>Additions to exploration and evaluation expenditures Note 6</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -48530,7 +48590,11 @@
           <t>Corporate, general and administrative expenses Note 19</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -48634,7 +48698,11 @@
           <t>Depreciation Note 6</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -51460,7 +51528,11 @@
           <t>Corporate, general and administrative expenses Note 18 $</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -51564,7 +51636,11 @@
           <t>Depreciation Note 6</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EMM.xlsx
+++ b/output/pdf_financials_xlsx/EMM.xlsx
@@ -1404,7 +1404,7 @@
         <v>-0.138651</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-1.803578</v>
+        <v>0.05</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2394,7 +2394,7 @@
         <v>100.4812047511722</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>99.27513297118421</v>
+        <v>2.752171876436289</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -4740,22 +4740,22 @@
         <v>0</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.45699</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>1.17679</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>1.018796</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>1.838862</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>1.734508</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.590351</v>
       </c>
     </row>
     <row r="68">
@@ -7643,10 +7643,10 @@
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.071548</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.04697</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -9086,30 +9086,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N130" s="3" t="n">
+        <v>0.008758</v>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>6.338927</v>
+      </c>
+      <c r="P130" s="3" t="n">
+        <v>20.250602</v>
+      </c>
+      <c r="Q130" s="3" t="n">
+        <v>11.676017</v>
+      </c>
+      <c r="R130" s="3" t="n">
+        <v>3.051144</v>
       </c>
       <c r="S130" s="1" t="inlineStr">
         <is>
@@ -9317,30 +9307,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N133" s="3" t="n">
+        <v>6.338927</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>20.072943</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>11.679138</v>
+      </c>
+      <c r="Q133" s="3" t="n">
+        <v>3.051158</v>
+      </c>
+      <c r="R133" s="3" t="n">
+        <v>13.182941</v>
       </c>
       <c r="S133" s="1" t="inlineStr">
         <is>
@@ -9370,10 +9350,10 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.071548</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.04697</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -9443,10 +9423,10 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.892697</v>
+        <v>-1.964245</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.828205</v>
+        <v>-2.875175</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-3.892825</v>
@@ -33760,7 +33740,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -42028,7 +42012,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -44800,7 +44788,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -46176,7 +46168,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -79064,7 +79060,11 @@
           <t>Income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D660" t="inlineStr"/>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E660" t="inlineStr">
         <is>
           <t>-</t>
